--- a/5.GUIDE-GLOBAL-CGE_v2_GreenEcos/Input_CGE/UserDefined.xlsx
+++ b/5.GUIDE-GLOBAL-CGE_v2_GreenEcos/Input_CGE/UserDefined.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kimc0\GUIDE_GLOBAL_CGE\2.GUIDE-GLOBAL-CGE_v2\Input_CGE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kimc0\GUIDE_GLOBAL_CGE\5.GUIDE-GLOBAL-CGE_v2_GreenEcos\Input_CGE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B589C1CF-9E1A-4648-BFEF-2806A8691BA7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2374BC8C-867B-411F-80F4-8BFC11014095}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9684" tabRatio="907" xr2:uid="{F15F39B2-9333-4C81-A44C-4FDD4B656403}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9684" tabRatio="907" activeTab="2" xr2:uid="{F15F39B2-9333-4C81-A44C-4FDD4B656403}"/>
   </bookViews>
   <sheets>
     <sheet name="CTAX_UserDefined" sheetId="29" r:id="rId1"/>
@@ -68,12 +68,6 @@
     <t>15_SAS</t>
   </si>
   <si>
-    <t>11_CAS</t>
-  </si>
-  <si>
-    <t>17_ANZ</t>
-  </si>
-  <si>
     <t>자동적 에너지 효율 개선</t>
   </si>
   <si>
@@ -83,16 +77,22 @@
     <t>*5%이상 값을 주기 어려움</t>
   </si>
   <si>
-    <t>14_CLV</t>
-  </si>
-  <si>
-    <t>16_APC</t>
-  </si>
-  <si>
     <t>*탄소 배출량 제약:2019년 1을 기준으로 각 연도, 지역별로 감축 수준을 지정함. 예제에서는 2030년 0.8, 2040년 0.6, 2060년 0.4를 가정함 (지역별로 동일함)</t>
   </si>
   <si>
     <t>*탄소가격: 2019년 0으로 2050년까지 선형적으로 증가하는 것으로 가정함. 예 2050년 2 는 200$ per tCO2를 의미함</t>
+  </si>
+  <si>
+    <t>11_RFSU</t>
+  </si>
+  <si>
+    <t>14_RCPA</t>
+  </si>
+  <si>
+    <t>16_RPAS</t>
+  </si>
+  <si>
+    <t>17_RPAO</t>
   </si>
 </sst>
 </file>
@@ -201,13 +201,13 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2858,7 +2858,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>11_CAS</c:v>
+                  <c:v>11_RFSU</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3644,7 +3644,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>14_CLV</c:v>
+                  <c:v>14_RCPA</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4172,7 +4172,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>16_APC</c:v>
+                  <c:v>16_RPAS</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4436,7 +4436,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>17_ANZ</c:v>
+                  <c:v>17_RPAO</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5890,123 +5890,123 @@
       <c r="B2" s="6">
         <v>0</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <f>B2+($AG2-$B2)/($AG$1-$B$1)</f>
         <v>6.4516129032258063E-2</v>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="11">
         <f t="shared" ref="D2:AF11" si="0">C2+($AG2-$B2)/($AG$1-$B$1)</f>
         <v>0.12903225806451613</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2" s="11">
         <f t="shared" si="0"/>
         <v>0.19354838709677419</v>
       </c>
-      <c r="F2" s="12">
+      <c r="F2" s="11">
         <f t="shared" si="0"/>
         <v>0.25806451612903225</v>
       </c>
-      <c r="G2" s="12">
+      <c r="G2" s="11">
         <f t="shared" si="0"/>
         <v>0.32258064516129031</v>
       </c>
-      <c r="H2" s="12">
+      <c r="H2" s="11">
         <f t="shared" si="0"/>
         <v>0.38709677419354838</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <f t="shared" si="0"/>
         <v>0.45161290322580644</v>
       </c>
-      <c r="J2" s="12">
+      <c r="J2" s="11">
         <f t="shared" si="0"/>
         <v>0.5161290322580645</v>
       </c>
-      <c r="K2" s="12">
+      <c r="K2" s="11">
         <f t="shared" si="0"/>
         <v>0.58064516129032251</v>
       </c>
-      <c r="L2" s="12">
+      <c r="L2" s="11">
         <f t="shared" si="0"/>
         <v>0.64516129032258052</v>
       </c>
-      <c r="M2" s="12">
+      <c r="M2" s="11">
         <f t="shared" si="0"/>
         <v>0.70967741935483852</v>
       </c>
-      <c r="N2" s="12">
+      <c r="N2" s="11">
         <f t="shared" si="0"/>
         <v>0.77419354838709653</v>
       </c>
-      <c r="O2" s="12">
+      <c r="O2" s="11">
         <f t="shared" si="0"/>
         <v>0.83870967741935454</v>
       </c>
-      <c r="P2" s="12">
+      <c r="P2" s="11">
         <f t="shared" si="0"/>
         <v>0.90322580645161255</v>
       </c>
-      <c r="Q2" s="12">
+      <c r="Q2" s="11">
         <f t="shared" si="0"/>
         <v>0.96774193548387055</v>
       </c>
-      <c r="R2" s="12">
+      <c r="R2" s="11">
         <f t="shared" si="0"/>
         <v>1.0322580645161286</v>
       </c>
-      <c r="S2" s="12">
+      <c r="S2" s="11">
         <f t="shared" si="0"/>
         <v>1.0967741935483866</v>
       </c>
-      <c r="T2" s="12">
+      <c r="T2" s="11">
         <f t="shared" si="0"/>
         <v>1.1612903225806446</v>
       </c>
-      <c r="U2" s="12">
+      <c r="U2" s="11">
         <f t="shared" si="0"/>
         <v>1.2258064516129026</v>
       </c>
-      <c r="V2" s="12">
+      <c r="V2" s="11">
         <f t="shared" si="0"/>
         <v>1.2903225806451606</v>
       </c>
-      <c r="W2" s="12">
+      <c r="W2" s="11">
         <f t="shared" si="0"/>
         <v>1.3548387096774186</v>
       </c>
-      <c r="X2" s="12">
+      <c r="X2" s="11">
         <f t="shared" si="0"/>
         <v>1.4193548387096766</v>
       </c>
-      <c r="Y2" s="12">
+      <c r="Y2" s="11">
         <f t="shared" si="0"/>
         <v>1.4838709677419346</v>
       </c>
-      <c r="Z2" s="12">
+      <c r="Z2" s="11">
         <f t="shared" si="0"/>
         <v>1.5483870967741926</v>
       </c>
-      <c r="AA2" s="12">
+      <c r="AA2" s="11">
         <f t="shared" si="0"/>
         <v>1.6129032258064506</v>
       </c>
-      <c r="AB2" s="12">
+      <c r="AB2" s="11">
         <f t="shared" si="0"/>
         <v>1.6774193548387086</v>
       </c>
-      <c r="AC2" s="12">
+      <c r="AC2" s="11">
         <f t="shared" si="0"/>
         <v>1.7419354838709666</v>
       </c>
-      <c r="AD2" s="12">
+      <c r="AD2" s="11">
         <f t="shared" si="0"/>
         <v>1.8064516129032246</v>
       </c>
-      <c r="AE2" s="12">
+      <c r="AE2" s="11">
         <f t="shared" si="0"/>
         <v>1.8709677419354827</v>
       </c>
-      <c r="AF2" s="12">
+      <c r="AF2" s="11">
         <f t="shared" si="0"/>
         <v>1.9354838709677407</v>
       </c>
@@ -6021,123 +6021,123 @@
       <c r="B3" s="6">
         <v>0</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="11">
         <f t="shared" ref="C3:R18" si="1">B3+($AG3-$B3)/($AG$1-$B$1)</f>
         <v>6.4516129032258063E-2</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="11">
         <f t="shared" si="1"/>
         <v>0.12903225806451613</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="11">
         <f t="shared" si="1"/>
         <v>0.19354838709677419</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="11">
         <f t="shared" si="1"/>
         <v>0.25806451612903225</v>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="11">
         <f t="shared" si="1"/>
         <v>0.32258064516129031</v>
       </c>
-      <c r="H3" s="12">
+      <c r="H3" s="11">
         <f t="shared" si="1"/>
         <v>0.38709677419354838</v>
       </c>
-      <c r="I3" s="12">
+      <c r="I3" s="11">
         <f t="shared" si="1"/>
         <v>0.45161290322580644</v>
       </c>
-      <c r="J3" s="12">
+      <c r="J3" s="11">
         <f t="shared" si="1"/>
         <v>0.5161290322580645</v>
       </c>
-      <c r="K3" s="12">
+      <c r="K3" s="11">
         <f t="shared" si="1"/>
         <v>0.58064516129032251</v>
       </c>
-      <c r="L3" s="12">
+      <c r="L3" s="11">
         <f t="shared" si="1"/>
         <v>0.64516129032258052</v>
       </c>
-      <c r="M3" s="12">
+      <c r="M3" s="11">
         <f t="shared" si="1"/>
         <v>0.70967741935483852</v>
       </c>
-      <c r="N3" s="12">
+      <c r="N3" s="11">
         <f t="shared" si="1"/>
         <v>0.77419354838709653</v>
       </c>
-      <c r="O3" s="12">
+      <c r="O3" s="11">
         <f t="shared" si="1"/>
         <v>0.83870967741935454</v>
       </c>
-      <c r="P3" s="12">
+      <c r="P3" s="11">
         <f t="shared" si="1"/>
         <v>0.90322580645161255</v>
       </c>
-      <c r="Q3" s="12">
+      <c r="Q3" s="11">
         <f t="shared" si="1"/>
         <v>0.96774193548387055</v>
       </c>
-      <c r="R3" s="12">
+      <c r="R3" s="11">
         <f t="shared" si="1"/>
         <v>1.0322580645161286</v>
       </c>
-      <c r="S3" s="12">
+      <c r="S3" s="11">
         <f t="shared" si="0"/>
         <v>1.0967741935483866</v>
       </c>
-      <c r="T3" s="12">
+      <c r="T3" s="11">
         <f t="shared" si="0"/>
         <v>1.1612903225806446</v>
       </c>
-      <c r="U3" s="12">
+      <c r="U3" s="11">
         <f t="shared" si="0"/>
         <v>1.2258064516129026</v>
       </c>
-      <c r="V3" s="12">
+      <c r="V3" s="11">
         <f t="shared" si="0"/>
         <v>1.2903225806451606</v>
       </c>
-      <c r="W3" s="12">
+      <c r="W3" s="11">
         <f t="shared" si="0"/>
         <v>1.3548387096774186</v>
       </c>
-      <c r="X3" s="12">
+      <c r="X3" s="11">
         <f t="shared" si="0"/>
         <v>1.4193548387096766</v>
       </c>
-      <c r="Y3" s="12">
+      <c r="Y3" s="11">
         <f t="shared" si="0"/>
         <v>1.4838709677419346</v>
       </c>
-      <c r="Z3" s="12">
+      <c r="Z3" s="11">
         <f t="shared" si="0"/>
         <v>1.5483870967741926</v>
       </c>
-      <c r="AA3" s="12">
+      <c r="AA3" s="11">
         <f t="shared" si="0"/>
         <v>1.6129032258064506</v>
       </c>
-      <c r="AB3" s="12">
+      <c r="AB3" s="11">
         <f t="shared" si="0"/>
         <v>1.6774193548387086</v>
       </c>
-      <c r="AC3" s="12">
+      <c r="AC3" s="11">
         <f t="shared" si="0"/>
         <v>1.7419354838709666</v>
       </c>
-      <c r="AD3" s="12">
+      <c r="AD3" s="11">
         <f t="shared" si="0"/>
         <v>1.8064516129032246</v>
       </c>
-      <c r="AE3" s="12">
+      <c r="AE3" s="11">
         <f t="shared" si="0"/>
         <v>1.8709677419354827</v>
       </c>
-      <c r="AF3" s="12">
+      <c r="AF3" s="11">
         <f t="shared" si="0"/>
         <v>1.9354838709677407</v>
       </c>
@@ -6152,123 +6152,123 @@
       <c r="B4" s="6">
         <v>0</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="11">
         <f t="shared" si="1"/>
         <v>6.4516129032258063E-2</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="11">
         <f t="shared" si="0"/>
         <v>0.12903225806451613</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="11">
         <f t="shared" si="0"/>
         <v>0.19354838709677419</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="11">
         <f t="shared" si="0"/>
         <v>0.25806451612903225</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="11">
         <f t="shared" si="0"/>
         <v>0.32258064516129031</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="11">
         <f t="shared" si="0"/>
         <v>0.38709677419354838</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="11">
         <f t="shared" si="0"/>
         <v>0.45161290322580644</v>
       </c>
-      <c r="J4" s="12">
+      <c r="J4" s="11">
         <f t="shared" si="0"/>
         <v>0.5161290322580645</v>
       </c>
-      <c r="K4" s="12">
+      <c r="K4" s="11">
         <f t="shared" si="0"/>
         <v>0.58064516129032251</v>
       </c>
-      <c r="L4" s="12">
+      <c r="L4" s="11">
         <f t="shared" si="0"/>
         <v>0.64516129032258052</v>
       </c>
-      <c r="M4" s="12">
+      <c r="M4" s="11">
         <f t="shared" si="0"/>
         <v>0.70967741935483852</v>
       </c>
-      <c r="N4" s="12">
+      <c r="N4" s="11">
         <f t="shared" si="0"/>
         <v>0.77419354838709653</v>
       </c>
-      <c r="O4" s="12">
+      <c r="O4" s="11">
         <f t="shared" si="0"/>
         <v>0.83870967741935454</v>
       </c>
-      <c r="P4" s="12">
+      <c r="P4" s="11">
         <f t="shared" si="0"/>
         <v>0.90322580645161255</v>
       </c>
-      <c r="Q4" s="12">
+      <c r="Q4" s="11">
         <f t="shared" si="0"/>
         <v>0.96774193548387055</v>
       </c>
-      <c r="R4" s="12">
+      <c r="R4" s="11">
         <f t="shared" si="0"/>
         <v>1.0322580645161286</v>
       </c>
-      <c r="S4" s="12">
+      <c r="S4" s="11">
         <f t="shared" si="0"/>
         <v>1.0967741935483866</v>
       </c>
-      <c r="T4" s="12">
+      <c r="T4" s="11">
         <f t="shared" si="0"/>
         <v>1.1612903225806446</v>
       </c>
-      <c r="U4" s="12">
+      <c r="U4" s="11">
         <f t="shared" si="0"/>
         <v>1.2258064516129026</v>
       </c>
-      <c r="V4" s="12">
+      <c r="V4" s="11">
         <f t="shared" si="0"/>
         <v>1.2903225806451606</v>
       </c>
-      <c r="W4" s="12">
+      <c r="W4" s="11">
         <f t="shared" si="0"/>
         <v>1.3548387096774186</v>
       </c>
-      <c r="X4" s="12">
+      <c r="X4" s="11">
         <f t="shared" si="0"/>
         <v>1.4193548387096766</v>
       </c>
-      <c r="Y4" s="12">
+      <c r="Y4" s="11">
         <f t="shared" si="0"/>
         <v>1.4838709677419346</v>
       </c>
-      <c r="Z4" s="12">
+      <c r="Z4" s="11">
         <f t="shared" si="0"/>
         <v>1.5483870967741926</v>
       </c>
-      <c r="AA4" s="12">
+      <c r="AA4" s="11">
         <f t="shared" si="0"/>
         <v>1.6129032258064506</v>
       </c>
-      <c r="AB4" s="12">
+      <c r="AB4" s="11">
         <f t="shared" si="0"/>
         <v>1.6774193548387086</v>
       </c>
-      <c r="AC4" s="12">
+      <c r="AC4" s="11">
         <f t="shared" si="0"/>
         <v>1.7419354838709666</v>
       </c>
-      <c r="AD4" s="12">
+      <c r="AD4" s="11">
         <f t="shared" si="0"/>
         <v>1.8064516129032246</v>
       </c>
-      <c r="AE4" s="12">
+      <c r="AE4" s="11">
         <f t="shared" si="0"/>
         <v>1.8709677419354827</v>
       </c>
-      <c r="AF4" s="12">
+      <c r="AF4" s="11">
         <f t="shared" si="0"/>
         <v>1.9354838709677407</v>
       </c>
@@ -6283,123 +6283,123 @@
       <c r="B5" s="6">
         <v>0</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="11">
         <f t="shared" si="1"/>
         <v>6.4516129032258063E-2</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="11">
         <f t="shared" si="0"/>
         <v>0.12903225806451613</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="11">
         <f t="shared" si="0"/>
         <v>0.19354838709677419</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="11">
         <f t="shared" si="0"/>
         <v>0.25806451612903225</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="11">
         <f t="shared" si="0"/>
         <v>0.32258064516129031</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="11">
         <f t="shared" si="0"/>
         <v>0.38709677419354838</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="11">
         <f t="shared" si="0"/>
         <v>0.45161290322580644</v>
       </c>
-      <c r="J5" s="12">
+      <c r="J5" s="11">
         <f t="shared" si="0"/>
         <v>0.5161290322580645</v>
       </c>
-      <c r="K5" s="12">
+      <c r="K5" s="11">
         <f t="shared" si="0"/>
         <v>0.58064516129032251</v>
       </c>
-      <c r="L5" s="12">
+      <c r="L5" s="11">
         <f t="shared" si="0"/>
         <v>0.64516129032258052</v>
       </c>
-      <c r="M5" s="12">
+      <c r="M5" s="11">
         <f t="shared" si="0"/>
         <v>0.70967741935483852</v>
       </c>
-      <c r="N5" s="12">
+      <c r="N5" s="11">
         <f t="shared" si="0"/>
         <v>0.77419354838709653</v>
       </c>
-      <c r="O5" s="12">
+      <c r="O5" s="11">
         <f t="shared" si="0"/>
         <v>0.83870967741935454</v>
       </c>
-      <c r="P5" s="12">
+      <c r="P5" s="11">
         <f t="shared" si="0"/>
         <v>0.90322580645161255</v>
       </c>
-      <c r="Q5" s="12">
+      <c r="Q5" s="11">
         <f t="shared" si="0"/>
         <v>0.96774193548387055</v>
       </c>
-      <c r="R5" s="12">
+      <c r="R5" s="11">
         <f t="shared" si="0"/>
         <v>1.0322580645161286</v>
       </c>
-      <c r="S5" s="12">
+      <c r="S5" s="11">
         <f t="shared" si="0"/>
         <v>1.0967741935483866</v>
       </c>
-      <c r="T5" s="12">
+      <c r="T5" s="11">
         <f t="shared" si="0"/>
         <v>1.1612903225806446</v>
       </c>
-      <c r="U5" s="12">
+      <c r="U5" s="11">
         <f t="shared" si="0"/>
         <v>1.2258064516129026</v>
       </c>
-      <c r="V5" s="12">
+      <c r="V5" s="11">
         <f t="shared" si="0"/>
         <v>1.2903225806451606</v>
       </c>
-      <c r="W5" s="12">
+      <c r="W5" s="11">
         <f t="shared" si="0"/>
         <v>1.3548387096774186</v>
       </c>
-      <c r="X5" s="12">
+      <c r="X5" s="11">
         <f t="shared" si="0"/>
         <v>1.4193548387096766</v>
       </c>
-      <c r="Y5" s="12">
+      <c r="Y5" s="11">
         <f t="shared" si="0"/>
         <v>1.4838709677419346</v>
       </c>
-      <c r="Z5" s="12">
+      <c r="Z5" s="11">
         <f t="shared" si="0"/>
         <v>1.5483870967741926</v>
       </c>
-      <c r="AA5" s="12">
+      <c r="AA5" s="11">
         <f t="shared" si="0"/>
         <v>1.6129032258064506</v>
       </c>
-      <c r="AB5" s="12">
+      <c r="AB5" s="11">
         <f t="shared" si="0"/>
         <v>1.6774193548387086</v>
       </c>
-      <c r="AC5" s="12">
+      <c r="AC5" s="11">
         <f t="shared" si="0"/>
         <v>1.7419354838709666</v>
       </c>
-      <c r="AD5" s="12">
+      <c r="AD5" s="11">
         <f t="shared" si="0"/>
         <v>1.8064516129032246</v>
       </c>
-      <c r="AE5" s="12">
+      <c r="AE5" s="11">
         <f t="shared" si="0"/>
         <v>1.8709677419354827</v>
       </c>
-      <c r="AF5" s="12">
+      <c r="AF5" s="11">
         <f t="shared" si="0"/>
         <v>1.9354838709677407</v>
       </c>
@@ -6414,123 +6414,123 @@
       <c r="B6" s="6">
         <v>0</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="11">
         <f t="shared" si="1"/>
         <v>6.4516129032258063E-2</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="11">
         <f t="shared" si="0"/>
         <v>0.12903225806451613</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="11">
         <f t="shared" si="0"/>
         <v>0.19354838709677419</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="11">
         <f t="shared" si="0"/>
         <v>0.25806451612903225</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="11">
         <f t="shared" si="0"/>
         <v>0.32258064516129031</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="11">
         <f t="shared" si="0"/>
         <v>0.38709677419354838</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="11">
         <f t="shared" si="0"/>
         <v>0.45161290322580644</v>
       </c>
-      <c r="J6" s="12">
+      <c r="J6" s="11">
         <f t="shared" si="0"/>
         <v>0.5161290322580645</v>
       </c>
-      <c r="K6" s="12">
+      <c r="K6" s="11">
         <f t="shared" si="0"/>
         <v>0.58064516129032251</v>
       </c>
-      <c r="L6" s="12">
+      <c r="L6" s="11">
         <f t="shared" si="0"/>
         <v>0.64516129032258052</v>
       </c>
-      <c r="M6" s="12">
+      <c r="M6" s="11">
         <f t="shared" si="0"/>
         <v>0.70967741935483852</v>
       </c>
-      <c r="N6" s="12">
+      <c r="N6" s="11">
         <f t="shared" si="0"/>
         <v>0.77419354838709653</v>
       </c>
-      <c r="O6" s="12">
+      <c r="O6" s="11">
         <f t="shared" si="0"/>
         <v>0.83870967741935454</v>
       </c>
-      <c r="P6" s="12">
+      <c r="P6" s="11">
         <f t="shared" si="0"/>
         <v>0.90322580645161255</v>
       </c>
-      <c r="Q6" s="12">
+      <c r="Q6" s="11">
         <f t="shared" si="0"/>
         <v>0.96774193548387055</v>
       </c>
-      <c r="R6" s="12">
+      <c r="R6" s="11">
         <f t="shared" si="0"/>
         <v>1.0322580645161286</v>
       </c>
-      <c r="S6" s="12">
+      <c r="S6" s="11">
         <f t="shared" si="0"/>
         <v>1.0967741935483866</v>
       </c>
-      <c r="T6" s="12">
+      <c r="T6" s="11">
         <f t="shared" si="0"/>
         <v>1.1612903225806446</v>
       </c>
-      <c r="U6" s="12">
+      <c r="U6" s="11">
         <f t="shared" si="0"/>
         <v>1.2258064516129026</v>
       </c>
-      <c r="V6" s="12">
+      <c r="V6" s="11">
         <f t="shared" si="0"/>
         <v>1.2903225806451606</v>
       </c>
-      <c r="W6" s="12">
+      <c r="W6" s="11">
         <f t="shared" si="0"/>
         <v>1.3548387096774186</v>
       </c>
-      <c r="X6" s="12">
+      <c r="X6" s="11">
         <f t="shared" si="0"/>
         <v>1.4193548387096766</v>
       </c>
-      <c r="Y6" s="12">
+      <c r="Y6" s="11">
         <f t="shared" si="0"/>
         <v>1.4838709677419346</v>
       </c>
-      <c r="Z6" s="12">
+      <c r="Z6" s="11">
         <f t="shared" si="0"/>
         <v>1.5483870967741926</v>
       </c>
-      <c r="AA6" s="12">
+      <c r="AA6" s="11">
         <f t="shared" si="0"/>
         <v>1.6129032258064506</v>
       </c>
-      <c r="AB6" s="12">
+      <c r="AB6" s="11">
         <f t="shared" si="0"/>
         <v>1.6774193548387086</v>
       </c>
-      <c r="AC6" s="12">
+      <c r="AC6" s="11">
         <f t="shared" si="0"/>
         <v>1.7419354838709666</v>
       </c>
-      <c r="AD6" s="12">
+      <c r="AD6" s="11">
         <f t="shared" si="0"/>
         <v>1.8064516129032246</v>
       </c>
-      <c r="AE6" s="12">
+      <c r="AE6" s="11">
         <f t="shared" si="0"/>
         <v>1.8709677419354827</v>
       </c>
-      <c r="AF6" s="12">
+      <c r="AF6" s="11">
         <f t="shared" si="0"/>
         <v>1.9354838709677407</v>
       </c>
@@ -6545,123 +6545,123 @@
       <c r="B7" s="6">
         <v>0</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="11">
         <f t="shared" si="1"/>
         <v>6.4516129032258063E-2</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="11">
         <f t="shared" si="0"/>
         <v>0.12903225806451613</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="11">
         <f t="shared" si="0"/>
         <v>0.19354838709677419</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="11">
         <f t="shared" si="0"/>
         <v>0.25806451612903225</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="11">
         <f t="shared" si="0"/>
         <v>0.32258064516129031</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="11">
         <f t="shared" si="0"/>
         <v>0.38709677419354838</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="11">
         <f t="shared" si="0"/>
         <v>0.45161290322580644</v>
       </c>
-      <c r="J7" s="12">
+      <c r="J7" s="11">
         <f t="shared" si="0"/>
         <v>0.5161290322580645</v>
       </c>
-      <c r="K7" s="12">
+      <c r="K7" s="11">
         <f t="shared" si="0"/>
         <v>0.58064516129032251</v>
       </c>
-      <c r="L7" s="12">
+      <c r="L7" s="11">
         <f t="shared" si="0"/>
         <v>0.64516129032258052</v>
       </c>
-      <c r="M7" s="12">
+      <c r="M7" s="11">
         <f t="shared" si="0"/>
         <v>0.70967741935483852</v>
       </c>
-      <c r="N7" s="12">
+      <c r="N7" s="11">
         <f t="shared" si="0"/>
         <v>0.77419354838709653</v>
       </c>
-      <c r="O7" s="12">
+      <c r="O7" s="11">
         <f t="shared" si="0"/>
         <v>0.83870967741935454</v>
       </c>
-      <c r="P7" s="12">
+      <c r="P7" s="11">
         <f t="shared" si="0"/>
         <v>0.90322580645161255</v>
       </c>
-      <c r="Q7" s="12">
+      <c r="Q7" s="11">
         <f t="shared" si="0"/>
         <v>0.96774193548387055</v>
       </c>
-      <c r="R7" s="12">
+      <c r="R7" s="11">
         <f t="shared" si="0"/>
         <v>1.0322580645161286</v>
       </c>
-      <c r="S7" s="12">
+      <c r="S7" s="11">
         <f t="shared" si="0"/>
         <v>1.0967741935483866</v>
       </c>
-      <c r="T7" s="12">
+      <c r="T7" s="11">
         <f t="shared" si="0"/>
         <v>1.1612903225806446</v>
       </c>
-      <c r="U7" s="12">
+      <c r="U7" s="11">
         <f t="shared" si="0"/>
         <v>1.2258064516129026</v>
       </c>
-      <c r="V7" s="12">
+      <c r="V7" s="11">
         <f t="shared" si="0"/>
         <v>1.2903225806451606</v>
       </c>
-      <c r="W7" s="12">
+      <c r="W7" s="11">
         <f t="shared" si="0"/>
         <v>1.3548387096774186</v>
       </c>
-      <c r="X7" s="12">
+      <c r="X7" s="11">
         <f t="shared" si="0"/>
         <v>1.4193548387096766</v>
       </c>
-      <c r="Y7" s="12">
+      <c r="Y7" s="11">
         <f t="shared" si="0"/>
         <v>1.4838709677419346</v>
       </c>
-      <c r="Z7" s="12">
+      <c r="Z7" s="11">
         <f t="shared" si="0"/>
         <v>1.5483870967741926</v>
       </c>
-      <c r="AA7" s="12">
+      <c r="AA7" s="11">
         <f t="shared" si="0"/>
         <v>1.6129032258064506</v>
       </c>
-      <c r="AB7" s="12">
+      <c r="AB7" s="11">
         <f t="shared" si="0"/>
         <v>1.6774193548387086</v>
       </c>
-      <c r="AC7" s="12">
+      <c r="AC7" s="11">
         <f t="shared" si="0"/>
         <v>1.7419354838709666</v>
       </c>
-      <c r="AD7" s="12">
+      <c r="AD7" s="11">
         <f t="shared" si="0"/>
         <v>1.8064516129032246</v>
       </c>
-      <c r="AE7" s="12">
+      <c r="AE7" s="11">
         <f t="shared" si="0"/>
         <v>1.8709677419354827</v>
       </c>
-      <c r="AF7" s="12">
+      <c r="AF7" s="11">
         <f t="shared" si="0"/>
         <v>1.9354838709677407</v>
       </c>
@@ -6676,123 +6676,123 @@
       <c r="B8" s="6">
         <v>0</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="11">
         <f t="shared" si="1"/>
         <v>6.4516129032258063E-2</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="11">
         <f t="shared" si="0"/>
         <v>0.12903225806451613</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="11">
         <f t="shared" si="0"/>
         <v>0.19354838709677419</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="11">
         <f t="shared" si="0"/>
         <v>0.25806451612903225</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="11">
         <f t="shared" si="0"/>
         <v>0.32258064516129031</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="11">
         <f t="shared" si="0"/>
         <v>0.38709677419354838</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="11">
         <f t="shared" si="0"/>
         <v>0.45161290322580644</v>
       </c>
-      <c r="J8" s="12">
+      <c r="J8" s="11">
         <f t="shared" si="0"/>
         <v>0.5161290322580645</v>
       </c>
-      <c r="K8" s="12">
+      <c r="K8" s="11">
         <f t="shared" si="0"/>
         <v>0.58064516129032251</v>
       </c>
-      <c r="L8" s="12">
+      <c r="L8" s="11">
         <f t="shared" si="0"/>
         <v>0.64516129032258052</v>
       </c>
-      <c r="M8" s="12">
+      <c r="M8" s="11">
         <f t="shared" si="0"/>
         <v>0.70967741935483852</v>
       </c>
-      <c r="N8" s="12">
+      <c r="N8" s="11">
         <f t="shared" si="0"/>
         <v>0.77419354838709653</v>
       </c>
-      <c r="O8" s="12">
+      <c r="O8" s="11">
         <f t="shared" si="0"/>
         <v>0.83870967741935454</v>
       </c>
-      <c r="P8" s="12">
+      <c r="P8" s="11">
         <f t="shared" si="0"/>
         <v>0.90322580645161255</v>
       </c>
-      <c r="Q8" s="12">
+      <c r="Q8" s="11">
         <f t="shared" si="0"/>
         <v>0.96774193548387055</v>
       </c>
-      <c r="R8" s="12">
+      <c r="R8" s="11">
         <f t="shared" si="0"/>
         <v>1.0322580645161286</v>
       </c>
-      <c r="S8" s="12">
+      <c r="S8" s="11">
         <f t="shared" si="0"/>
         <v>1.0967741935483866</v>
       </c>
-      <c r="T8" s="12">
+      <c r="T8" s="11">
         <f t="shared" si="0"/>
         <v>1.1612903225806446</v>
       </c>
-      <c r="U8" s="12">
+      <c r="U8" s="11">
         <f t="shared" si="0"/>
         <v>1.2258064516129026</v>
       </c>
-      <c r="V8" s="12">
+      <c r="V8" s="11">
         <f t="shared" si="0"/>
         <v>1.2903225806451606</v>
       </c>
-      <c r="W8" s="12">
+      <c r="W8" s="11">
         <f t="shared" si="0"/>
         <v>1.3548387096774186</v>
       </c>
-      <c r="X8" s="12">
+      <c r="X8" s="11">
         <f t="shared" si="0"/>
         <v>1.4193548387096766</v>
       </c>
-      <c r="Y8" s="12">
+      <c r="Y8" s="11">
         <f t="shared" si="0"/>
         <v>1.4838709677419346</v>
       </c>
-      <c r="Z8" s="12">
+      <c r="Z8" s="11">
         <f t="shared" si="0"/>
         <v>1.5483870967741926</v>
       </c>
-      <c r="AA8" s="12">
+      <c r="AA8" s="11">
         <f t="shared" si="0"/>
         <v>1.6129032258064506</v>
       </c>
-      <c r="AB8" s="12">
+      <c r="AB8" s="11">
         <f t="shared" si="0"/>
         <v>1.6774193548387086</v>
       </c>
-      <c r="AC8" s="12">
+      <c r="AC8" s="11">
         <f t="shared" si="0"/>
         <v>1.7419354838709666</v>
       </c>
-      <c r="AD8" s="12">
+      <c r="AD8" s="11">
         <f t="shared" si="0"/>
         <v>1.8064516129032246</v>
       </c>
-      <c r="AE8" s="12">
+      <c r="AE8" s="11">
         <f t="shared" si="0"/>
         <v>1.8709677419354827</v>
       </c>
-      <c r="AF8" s="12">
+      <c r="AF8" s="11">
         <f t="shared" si="0"/>
         <v>1.9354838709677407</v>
       </c>
@@ -6807,123 +6807,123 @@
       <c r="B9" s="6">
         <v>0</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="11">
         <f t="shared" si="1"/>
         <v>6.4516129032258063E-2</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="11">
         <f t="shared" si="0"/>
         <v>0.12903225806451613</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="11">
         <f t="shared" si="0"/>
         <v>0.19354838709677419</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="11">
         <f t="shared" si="0"/>
         <v>0.25806451612903225</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="11">
         <f t="shared" si="0"/>
         <v>0.32258064516129031</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="11">
         <f t="shared" si="0"/>
         <v>0.38709677419354838</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="11">
         <f t="shared" si="0"/>
         <v>0.45161290322580644</v>
       </c>
-      <c r="J9" s="12">
+      <c r="J9" s="11">
         <f t="shared" si="0"/>
         <v>0.5161290322580645</v>
       </c>
-      <c r="K9" s="12">
+      <c r="K9" s="11">
         <f t="shared" si="0"/>
         <v>0.58064516129032251</v>
       </c>
-      <c r="L9" s="12">
+      <c r="L9" s="11">
         <f t="shared" si="0"/>
         <v>0.64516129032258052</v>
       </c>
-      <c r="M9" s="12">
+      <c r="M9" s="11">
         <f t="shared" si="0"/>
         <v>0.70967741935483852</v>
       </c>
-      <c r="N9" s="12">
+      <c r="N9" s="11">
         <f t="shared" si="0"/>
         <v>0.77419354838709653</v>
       </c>
-      <c r="O9" s="12">
+      <c r="O9" s="11">
         <f t="shared" si="0"/>
         <v>0.83870967741935454</v>
       </c>
-      <c r="P9" s="12">
+      <c r="P9" s="11">
         <f t="shared" si="0"/>
         <v>0.90322580645161255</v>
       </c>
-      <c r="Q9" s="12">
+      <c r="Q9" s="11">
         <f t="shared" si="0"/>
         <v>0.96774193548387055</v>
       </c>
-      <c r="R9" s="12">
+      <c r="R9" s="11">
         <f t="shared" si="0"/>
         <v>1.0322580645161286</v>
       </c>
-      <c r="S9" s="12">
+      <c r="S9" s="11">
         <f t="shared" si="0"/>
         <v>1.0967741935483866</v>
       </c>
-      <c r="T9" s="12">
+      <c r="T9" s="11">
         <f t="shared" si="0"/>
         <v>1.1612903225806446</v>
       </c>
-      <c r="U9" s="12">
+      <c r="U9" s="11">
         <f t="shared" si="0"/>
         <v>1.2258064516129026</v>
       </c>
-      <c r="V9" s="12">
+      <c r="V9" s="11">
         <f t="shared" si="0"/>
         <v>1.2903225806451606</v>
       </c>
-      <c r="W9" s="12">
+      <c r="W9" s="11">
         <f t="shared" si="0"/>
         <v>1.3548387096774186</v>
       </c>
-      <c r="X9" s="12">
+      <c r="X9" s="11">
         <f t="shared" si="0"/>
         <v>1.4193548387096766</v>
       </c>
-      <c r="Y9" s="12">
+      <c r="Y9" s="11">
         <f t="shared" si="0"/>
         <v>1.4838709677419346</v>
       </c>
-      <c r="Z9" s="12">
+      <c r="Z9" s="11">
         <f t="shared" si="0"/>
         <v>1.5483870967741926</v>
       </c>
-      <c r="AA9" s="12">
+      <c r="AA9" s="11">
         <f t="shared" si="0"/>
         <v>1.6129032258064506</v>
       </c>
-      <c r="AB9" s="12">
+      <c r="AB9" s="11">
         <f t="shared" si="0"/>
         <v>1.6774193548387086</v>
       </c>
-      <c r="AC9" s="12">
+      <c r="AC9" s="11">
         <f t="shared" si="0"/>
         <v>1.7419354838709666</v>
       </c>
-      <c r="AD9" s="12">
+      <c r="AD9" s="11">
         <f t="shared" si="0"/>
         <v>1.8064516129032246</v>
       </c>
-      <c r="AE9" s="12">
+      <c r="AE9" s="11">
         <f t="shared" si="0"/>
         <v>1.8709677419354827</v>
       </c>
-      <c r="AF9" s="12">
+      <c r="AF9" s="11">
         <f t="shared" si="0"/>
         <v>1.9354838709677407</v>
       </c>
@@ -6938,123 +6938,123 @@
       <c r="B10" s="6">
         <v>0</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="11">
         <f t="shared" si="1"/>
         <v>6.4516129032258063E-2</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="11">
         <f t="shared" si="0"/>
         <v>0.12903225806451613</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="11">
         <f t="shared" si="0"/>
         <v>0.19354838709677419</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="11">
         <f t="shared" si="0"/>
         <v>0.25806451612903225</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="11">
         <f t="shared" si="0"/>
         <v>0.32258064516129031</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="11">
         <f t="shared" si="0"/>
         <v>0.38709677419354838</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="11">
         <f t="shared" si="0"/>
         <v>0.45161290322580644</v>
       </c>
-      <c r="J10" s="12">
+      <c r="J10" s="11">
         <f t="shared" si="0"/>
         <v>0.5161290322580645</v>
       </c>
-      <c r="K10" s="12">
+      <c r="K10" s="11">
         <f t="shared" si="0"/>
         <v>0.58064516129032251</v>
       </c>
-      <c r="L10" s="12">
+      <c r="L10" s="11">
         <f t="shared" si="0"/>
         <v>0.64516129032258052</v>
       </c>
-      <c r="M10" s="12">
+      <c r="M10" s="11">
         <f t="shared" si="0"/>
         <v>0.70967741935483852</v>
       </c>
-      <c r="N10" s="12">
+      <c r="N10" s="11">
         <f t="shared" si="0"/>
         <v>0.77419354838709653</v>
       </c>
-      <c r="O10" s="12">
+      <c r="O10" s="11">
         <f t="shared" si="0"/>
         <v>0.83870967741935454</v>
       </c>
-      <c r="P10" s="12">
+      <c r="P10" s="11">
         <f t="shared" si="0"/>
         <v>0.90322580645161255</v>
       </c>
-      <c r="Q10" s="12">
+      <c r="Q10" s="11">
         <f t="shared" si="0"/>
         <v>0.96774193548387055</v>
       </c>
-      <c r="R10" s="12">
+      <c r="R10" s="11">
         <f t="shared" si="0"/>
         <v>1.0322580645161286</v>
       </c>
-      <c r="S10" s="12">
+      <c r="S10" s="11">
         <f t="shared" si="0"/>
         <v>1.0967741935483866</v>
       </c>
-      <c r="T10" s="12">
+      <c r="T10" s="11">
         <f t="shared" si="0"/>
         <v>1.1612903225806446</v>
       </c>
-      <c r="U10" s="12">
+      <c r="U10" s="11">
         <f t="shared" si="0"/>
         <v>1.2258064516129026</v>
       </c>
-      <c r="V10" s="12">
+      <c r="V10" s="11">
         <f t="shared" si="0"/>
         <v>1.2903225806451606</v>
       </c>
-      <c r="W10" s="12">
+      <c r="W10" s="11">
         <f t="shared" si="0"/>
         <v>1.3548387096774186</v>
       </c>
-      <c r="X10" s="12">
+      <c r="X10" s="11">
         <f t="shared" si="0"/>
         <v>1.4193548387096766</v>
       </c>
-      <c r="Y10" s="12">
+      <c r="Y10" s="11">
         <f t="shared" si="0"/>
         <v>1.4838709677419346</v>
       </c>
-      <c r="Z10" s="12">
+      <c r="Z10" s="11">
         <f t="shared" si="0"/>
         <v>1.5483870967741926</v>
       </c>
-      <c r="AA10" s="12">
+      <c r="AA10" s="11">
         <f t="shared" si="0"/>
         <v>1.6129032258064506</v>
       </c>
-      <c r="AB10" s="12">
+      <c r="AB10" s="11">
         <f t="shared" si="0"/>
         <v>1.6774193548387086</v>
       </c>
-      <c r="AC10" s="12">
+      <c r="AC10" s="11">
         <f t="shared" si="0"/>
         <v>1.7419354838709666</v>
       </c>
-      <c r="AD10" s="12">
+      <c r="AD10" s="11">
         <f t="shared" si="0"/>
         <v>1.8064516129032246</v>
       </c>
-      <c r="AE10" s="12">
+      <c r="AE10" s="11">
         <f t="shared" si="0"/>
         <v>1.8709677419354827</v>
       </c>
-      <c r="AF10" s="12">
+      <c r="AF10" s="11">
         <f t="shared" si="0"/>
         <v>1.9354838709677407</v>
       </c>
@@ -7069,123 +7069,123 @@
       <c r="B11" s="6">
         <v>0</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="11">
         <f t="shared" si="1"/>
         <v>6.4516129032258063E-2</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="11">
         <f t="shared" si="0"/>
         <v>0.12903225806451613</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="11">
         <f t="shared" si="0"/>
         <v>0.19354838709677419</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="11">
         <f t="shared" si="0"/>
         <v>0.25806451612903225</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="11">
         <f t="shared" si="0"/>
         <v>0.32258064516129031</v>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="11">
         <f t="shared" si="0"/>
         <v>0.38709677419354838</v>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="11">
         <f t="shared" si="0"/>
         <v>0.45161290322580644</v>
       </c>
-      <c r="J11" s="12">
+      <c r="J11" s="11">
         <f t="shared" si="0"/>
         <v>0.5161290322580645</v>
       </c>
-      <c r="K11" s="12">
+      <c r="K11" s="11">
         <f t="shared" si="0"/>
         <v>0.58064516129032251</v>
       </c>
-      <c r="L11" s="12">
+      <c r="L11" s="11">
         <f t="shared" si="0"/>
         <v>0.64516129032258052</v>
       </c>
-      <c r="M11" s="12">
+      <c r="M11" s="11">
         <f t="shared" ref="D11:AF18" si="2">L11+($AG11-$B11)/($AG$1-$B$1)</f>
         <v>0.70967741935483852</v>
       </c>
-      <c r="N11" s="12">
+      <c r="N11" s="11">
         <f t="shared" si="2"/>
         <v>0.77419354838709653</v>
       </c>
-      <c r="O11" s="12">
+      <c r="O11" s="11">
         <f t="shared" si="2"/>
         <v>0.83870967741935454</v>
       </c>
-      <c r="P11" s="12">
+      <c r="P11" s="11">
         <f t="shared" si="2"/>
         <v>0.90322580645161255</v>
       </c>
-      <c r="Q11" s="12">
+      <c r="Q11" s="11">
         <f t="shared" si="2"/>
         <v>0.96774193548387055</v>
       </c>
-      <c r="R11" s="12">
+      <c r="R11" s="11">
         <f t="shared" si="2"/>
         <v>1.0322580645161286</v>
       </c>
-      <c r="S11" s="12">
+      <c r="S11" s="11">
         <f t="shared" si="2"/>
         <v>1.0967741935483866</v>
       </c>
-      <c r="T11" s="12">
+      <c r="T11" s="11">
         <f t="shared" si="2"/>
         <v>1.1612903225806446</v>
       </c>
-      <c r="U11" s="12">
+      <c r="U11" s="11">
         <f t="shared" si="2"/>
         <v>1.2258064516129026</v>
       </c>
-      <c r="V11" s="12">
+      <c r="V11" s="11">
         <f t="shared" si="2"/>
         <v>1.2903225806451606</v>
       </c>
-      <c r="W11" s="12">
+      <c r="W11" s="11">
         <f t="shared" si="2"/>
         <v>1.3548387096774186</v>
       </c>
-      <c r="X11" s="12">
+      <c r="X11" s="11">
         <f t="shared" si="2"/>
         <v>1.4193548387096766</v>
       </c>
-      <c r="Y11" s="12">
+      <c r="Y11" s="11">
         <f t="shared" si="2"/>
         <v>1.4838709677419346</v>
       </c>
-      <c r="Z11" s="12">
+      <c r="Z11" s="11">
         <f t="shared" si="2"/>
         <v>1.5483870967741926</v>
       </c>
-      <c r="AA11" s="12">
+      <c r="AA11" s="11">
         <f t="shared" si="2"/>
         <v>1.6129032258064506</v>
       </c>
-      <c r="AB11" s="12">
+      <c r="AB11" s="11">
         <f t="shared" si="2"/>
         <v>1.6774193548387086</v>
       </c>
-      <c r="AC11" s="12">
+      <c r="AC11" s="11">
         <f t="shared" si="2"/>
         <v>1.7419354838709666</v>
       </c>
-      <c r="AD11" s="12">
+      <c r="AD11" s="11">
         <f t="shared" si="2"/>
         <v>1.8064516129032246</v>
       </c>
-      <c r="AE11" s="12">
+      <c r="AE11" s="11">
         <f t="shared" si="2"/>
         <v>1.8709677419354827</v>
       </c>
-      <c r="AF11" s="12">
+      <c r="AF11" s="11">
         <f t="shared" si="2"/>
         <v>1.9354838709677407</v>
       </c>
@@ -7195,128 +7195,128 @@
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B12" s="6">
         <v>0</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="11">
         <f t="shared" si="1"/>
         <v>6.4516129032258063E-2</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="11">
         <f t="shared" si="2"/>
         <v>0.12903225806451613</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="11">
         <f t="shared" si="2"/>
         <v>0.19354838709677419</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="11">
         <f t="shared" si="2"/>
         <v>0.25806451612903225</v>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="11">
         <f t="shared" si="2"/>
         <v>0.32258064516129031</v>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="11">
         <f t="shared" si="2"/>
         <v>0.38709677419354838</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="11">
         <f t="shared" si="2"/>
         <v>0.45161290322580644</v>
       </c>
-      <c r="J12" s="12">
+      <c r="J12" s="11">
         <f t="shared" si="2"/>
         <v>0.5161290322580645</v>
       </c>
-      <c r="K12" s="12">
+      <c r="K12" s="11">
         <f t="shared" si="2"/>
         <v>0.58064516129032251</v>
       </c>
-      <c r="L12" s="12">
+      <c r="L12" s="11">
         <f t="shared" si="2"/>
         <v>0.64516129032258052</v>
       </c>
-      <c r="M12" s="12">
+      <c r="M12" s="11">
         <f t="shared" si="2"/>
         <v>0.70967741935483852</v>
       </c>
-      <c r="N12" s="12">
+      <c r="N12" s="11">
         <f t="shared" si="2"/>
         <v>0.77419354838709653</v>
       </c>
-      <c r="O12" s="12">
+      <c r="O12" s="11">
         <f t="shared" si="2"/>
         <v>0.83870967741935454</v>
       </c>
-      <c r="P12" s="12">
+      <c r="P12" s="11">
         <f t="shared" si="2"/>
         <v>0.90322580645161255</v>
       </c>
-      <c r="Q12" s="12">
+      <c r="Q12" s="11">
         <f t="shared" si="2"/>
         <v>0.96774193548387055</v>
       </c>
-      <c r="R12" s="12">
+      <c r="R12" s="11">
         <f t="shared" si="2"/>
         <v>1.0322580645161286</v>
       </c>
-      <c r="S12" s="12">
+      <c r="S12" s="11">
         <f t="shared" si="2"/>
         <v>1.0967741935483866</v>
       </c>
-      <c r="T12" s="12">
+      <c r="T12" s="11">
         <f t="shared" si="2"/>
         <v>1.1612903225806446</v>
       </c>
-      <c r="U12" s="12">
+      <c r="U12" s="11">
         <f t="shared" si="2"/>
         <v>1.2258064516129026</v>
       </c>
-      <c r="V12" s="12">
+      <c r="V12" s="11">
         <f t="shared" si="2"/>
         <v>1.2903225806451606</v>
       </c>
-      <c r="W12" s="12">
+      <c r="W12" s="11">
         <f t="shared" si="2"/>
         <v>1.3548387096774186</v>
       </c>
-      <c r="X12" s="12">
+      <c r="X12" s="11">
         <f t="shared" si="2"/>
         <v>1.4193548387096766</v>
       </c>
-      <c r="Y12" s="12">
+      <c r="Y12" s="11">
         <f t="shared" si="2"/>
         <v>1.4838709677419346</v>
       </c>
-      <c r="Z12" s="12">
+      <c r="Z12" s="11">
         <f t="shared" si="2"/>
         <v>1.5483870967741926</v>
       </c>
-      <c r="AA12" s="12">
+      <c r="AA12" s="11">
         <f t="shared" si="2"/>
         <v>1.6129032258064506</v>
       </c>
-      <c r="AB12" s="12">
+      <c r="AB12" s="11">
         <f t="shared" si="2"/>
         <v>1.6774193548387086</v>
       </c>
-      <c r="AC12" s="12">
+      <c r="AC12" s="11">
         <f t="shared" si="2"/>
         <v>1.7419354838709666</v>
       </c>
-      <c r="AD12" s="12">
+      <c r="AD12" s="11">
         <f t="shared" si="2"/>
         <v>1.8064516129032246</v>
       </c>
-      <c r="AE12" s="12">
+      <c r="AE12" s="11">
         <f t="shared" si="2"/>
         <v>1.8709677419354827</v>
       </c>
-      <c r="AF12" s="12">
+      <c r="AF12" s="11">
         <f t="shared" si="2"/>
         <v>1.9354838709677407</v>
       </c>
@@ -7331,123 +7331,123 @@
       <c r="B13" s="6">
         <v>0</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="11">
         <f t="shared" si="1"/>
         <v>6.4516129032258063E-2</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="11">
         <f t="shared" si="2"/>
         <v>0.12903225806451613</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="11">
         <f t="shared" si="2"/>
         <v>0.19354838709677419</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="11">
         <f t="shared" si="2"/>
         <v>0.25806451612903225</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="11">
         <f t="shared" si="2"/>
         <v>0.32258064516129031</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="11">
         <f t="shared" si="2"/>
         <v>0.38709677419354838</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="11">
         <f t="shared" si="2"/>
         <v>0.45161290322580644</v>
       </c>
-      <c r="J13" s="12">
+      <c r="J13" s="11">
         <f t="shared" si="2"/>
         <v>0.5161290322580645</v>
       </c>
-      <c r="K13" s="12">
+      <c r="K13" s="11">
         <f t="shared" si="2"/>
         <v>0.58064516129032251</v>
       </c>
-      <c r="L13" s="12">
+      <c r="L13" s="11">
         <f t="shared" si="2"/>
         <v>0.64516129032258052</v>
       </c>
-      <c r="M13" s="12">
+      <c r="M13" s="11">
         <f t="shared" si="2"/>
         <v>0.70967741935483852</v>
       </c>
-      <c r="N13" s="12">
+      <c r="N13" s="11">
         <f t="shared" si="2"/>
         <v>0.77419354838709653</v>
       </c>
-      <c r="O13" s="12">
+      <c r="O13" s="11">
         <f t="shared" si="2"/>
         <v>0.83870967741935454</v>
       </c>
-      <c r="P13" s="12">
+      <c r="P13" s="11">
         <f t="shared" si="2"/>
         <v>0.90322580645161255</v>
       </c>
-      <c r="Q13" s="12">
+      <c r="Q13" s="11">
         <f t="shared" si="2"/>
         <v>0.96774193548387055</v>
       </c>
-      <c r="R13" s="12">
+      <c r="R13" s="11">
         <f t="shared" si="2"/>
         <v>1.0322580645161286</v>
       </c>
-      <c r="S13" s="12">
+      <c r="S13" s="11">
         <f t="shared" si="2"/>
         <v>1.0967741935483866</v>
       </c>
-      <c r="T13" s="12">
+      <c r="T13" s="11">
         <f t="shared" si="2"/>
         <v>1.1612903225806446</v>
       </c>
-      <c r="U13" s="12">
+      <c r="U13" s="11">
         <f t="shared" si="2"/>
         <v>1.2258064516129026</v>
       </c>
-      <c r="V13" s="12">
+      <c r="V13" s="11">
         <f t="shared" si="2"/>
         <v>1.2903225806451606</v>
       </c>
-      <c r="W13" s="12">
+      <c r="W13" s="11">
         <f t="shared" si="2"/>
         <v>1.3548387096774186</v>
       </c>
-      <c r="X13" s="12">
+      <c r="X13" s="11">
         <f t="shared" si="2"/>
         <v>1.4193548387096766</v>
       </c>
-      <c r="Y13" s="12">
+      <c r="Y13" s="11">
         <f t="shared" si="2"/>
         <v>1.4838709677419346</v>
       </c>
-      <c r="Z13" s="12">
+      <c r="Z13" s="11">
         <f t="shared" si="2"/>
         <v>1.5483870967741926</v>
       </c>
-      <c r="AA13" s="12">
+      <c r="AA13" s="11">
         <f t="shared" si="2"/>
         <v>1.6129032258064506</v>
       </c>
-      <c r="AB13" s="12">
+      <c r="AB13" s="11">
         <f t="shared" si="2"/>
         <v>1.6774193548387086</v>
       </c>
-      <c r="AC13" s="12">
+      <c r="AC13" s="11">
         <f t="shared" si="2"/>
         <v>1.7419354838709666</v>
       </c>
-      <c r="AD13" s="12">
+      <c r="AD13" s="11">
         <f t="shared" si="2"/>
         <v>1.8064516129032246</v>
       </c>
-      <c r="AE13" s="12">
+      <c r="AE13" s="11">
         <f t="shared" si="2"/>
         <v>1.8709677419354827</v>
       </c>
-      <c r="AF13" s="12">
+      <c r="AF13" s="11">
         <f t="shared" si="2"/>
         <v>1.9354838709677407</v>
       </c>
@@ -7462,123 +7462,123 @@
       <c r="B14" s="6">
         <v>0</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="11">
         <f t="shared" si="1"/>
         <v>6.4516129032258063E-2</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="11">
         <f t="shared" si="2"/>
         <v>0.12903225806451613</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="11">
         <f t="shared" si="2"/>
         <v>0.19354838709677419</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="11">
         <f t="shared" si="2"/>
         <v>0.25806451612903225</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="11">
         <f t="shared" si="2"/>
         <v>0.32258064516129031</v>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="11">
         <f t="shared" si="2"/>
         <v>0.38709677419354838</v>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="11">
         <f t="shared" si="2"/>
         <v>0.45161290322580644</v>
       </c>
-      <c r="J14" s="12">
+      <c r="J14" s="11">
         <f t="shared" si="2"/>
         <v>0.5161290322580645</v>
       </c>
-      <c r="K14" s="12">
+      <c r="K14" s="11">
         <f t="shared" si="2"/>
         <v>0.58064516129032251</v>
       </c>
-      <c r="L14" s="12">
+      <c r="L14" s="11">
         <f t="shared" si="2"/>
         <v>0.64516129032258052</v>
       </c>
-      <c r="M14" s="12">
+      <c r="M14" s="11">
         <f t="shared" si="2"/>
         <v>0.70967741935483852</v>
       </c>
-      <c r="N14" s="12">
+      <c r="N14" s="11">
         <f t="shared" si="2"/>
         <v>0.77419354838709653</v>
       </c>
-      <c r="O14" s="12">
+      <c r="O14" s="11">
         <f t="shared" si="2"/>
         <v>0.83870967741935454</v>
       </c>
-      <c r="P14" s="12">
+      <c r="P14" s="11">
         <f t="shared" si="2"/>
         <v>0.90322580645161255</v>
       </c>
-      <c r="Q14" s="12">
+      <c r="Q14" s="11">
         <f t="shared" si="2"/>
         <v>0.96774193548387055</v>
       </c>
-      <c r="R14" s="12">
+      <c r="R14" s="11">
         <f t="shared" si="2"/>
         <v>1.0322580645161286</v>
       </c>
-      <c r="S14" s="12">
+      <c r="S14" s="11">
         <f t="shared" si="2"/>
         <v>1.0967741935483866</v>
       </c>
-      <c r="T14" s="12">
+      <c r="T14" s="11">
         <f t="shared" si="2"/>
         <v>1.1612903225806446</v>
       </c>
-      <c r="U14" s="12">
+      <c r="U14" s="11">
         <f t="shared" si="2"/>
         <v>1.2258064516129026</v>
       </c>
-      <c r="V14" s="12">
+      <c r="V14" s="11">
         <f t="shared" si="2"/>
         <v>1.2903225806451606</v>
       </c>
-      <c r="W14" s="12">
+      <c r="W14" s="11">
         <f t="shared" si="2"/>
         <v>1.3548387096774186</v>
       </c>
-      <c r="X14" s="12">
+      <c r="X14" s="11">
         <f t="shared" si="2"/>
         <v>1.4193548387096766</v>
       </c>
-      <c r="Y14" s="12">
+      <c r="Y14" s="11">
         <f t="shared" si="2"/>
         <v>1.4838709677419346</v>
       </c>
-      <c r="Z14" s="12">
+      <c r="Z14" s="11">
         <f t="shared" si="2"/>
         <v>1.5483870967741926</v>
       </c>
-      <c r="AA14" s="12">
+      <c r="AA14" s="11">
         <f t="shared" si="2"/>
         <v>1.6129032258064506</v>
       </c>
-      <c r="AB14" s="12">
+      <c r="AB14" s="11">
         <f t="shared" si="2"/>
         <v>1.6774193548387086</v>
       </c>
-      <c r="AC14" s="12">
+      <c r="AC14" s="11">
         <f t="shared" si="2"/>
         <v>1.7419354838709666</v>
       </c>
-      <c r="AD14" s="12">
+      <c r="AD14" s="11">
         <f t="shared" si="2"/>
         <v>1.8064516129032246</v>
       </c>
-      <c r="AE14" s="12">
+      <c r="AE14" s="11">
         <f t="shared" si="2"/>
         <v>1.8709677419354827</v>
       </c>
-      <c r="AF14" s="12">
+      <c r="AF14" s="11">
         <f t="shared" si="2"/>
         <v>1.9354838709677407</v>
       </c>
@@ -7588,128 +7588,128 @@
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15" s="6">
         <v>0</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="11">
         <f t="shared" si="1"/>
         <v>6.4516129032258063E-2</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="11">
         <f t="shared" si="2"/>
         <v>0.12903225806451613</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="11">
         <f t="shared" si="2"/>
         <v>0.19354838709677419</v>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="11">
         <f t="shared" si="2"/>
         <v>0.25806451612903225</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="11">
         <f t="shared" si="2"/>
         <v>0.32258064516129031</v>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="11">
         <f t="shared" si="2"/>
         <v>0.38709677419354838</v>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="11">
         <f t="shared" si="2"/>
         <v>0.45161290322580644</v>
       </c>
-      <c r="J15" s="12">
+      <c r="J15" s="11">
         <f t="shared" si="2"/>
         <v>0.5161290322580645</v>
       </c>
-      <c r="K15" s="12">
+      <c r="K15" s="11">
         <f t="shared" si="2"/>
         <v>0.58064516129032251</v>
       </c>
-      <c r="L15" s="12">
+      <c r="L15" s="11">
         <f t="shared" si="2"/>
         <v>0.64516129032258052</v>
       </c>
-      <c r="M15" s="12">
+      <c r="M15" s="11">
         <f t="shared" si="2"/>
         <v>0.70967741935483852</v>
       </c>
-      <c r="N15" s="12">
+      <c r="N15" s="11">
         <f t="shared" si="2"/>
         <v>0.77419354838709653</v>
       </c>
-      <c r="O15" s="12">
+      <c r="O15" s="11">
         <f t="shared" si="2"/>
         <v>0.83870967741935454</v>
       </c>
-      <c r="P15" s="12">
+      <c r="P15" s="11">
         <f t="shared" si="2"/>
         <v>0.90322580645161255</v>
       </c>
-      <c r="Q15" s="12">
+      <c r="Q15" s="11">
         <f t="shared" si="2"/>
         <v>0.96774193548387055</v>
       </c>
-      <c r="R15" s="12">
+      <c r="R15" s="11">
         <f t="shared" si="2"/>
         <v>1.0322580645161286</v>
       </c>
-      <c r="S15" s="12">
+      <c r="S15" s="11">
         <f t="shared" si="2"/>
         <v>1.0967741935483866</v>
       </c>
-      <c r="T15" s="12">
+      <c r="T15" s="11">
         <f t="shared" si="2"/>
         <v>1.1612903225806446</v>
       </c>
-      <c r="U15" s="12">
+      <c r="U15" s="11">
         <f t="shared" si="2"/>
         <v>1.2258064516129026</v>
       </c>
-      <c r="V15" s="12">
+      <c r="V15" s="11">
         <f t="shared" si="2"/>
         <v>1.2903225806451606</v>
       </c>
-      <c r="W15" s="12">
+      <c r="W15" s="11">
         <f t="shared" si="2"/>
         <v>1.3548387096774186</v>
       </c>
-      <c r="X15" s="12">
+      <c r="X15" s="11">
         <f t="shared" si="2"/>
         <v>1.4193548387096766</v>
       </c>
-      <c r="Y15" s="12">
+      <c r="Y15" s="11">
         <f t="shared" si="2"/>
         <v>1.4838709677419346</v>
       </c>
-      <c r="Z15" s="12">
+      <c r="Z15" s="11">
         <f t="shared" si="2"/>
         <v>1.5483870967741926</v>
       </c>
-      <c r="AA15" s="12">
+      <c r="AA15" s="11">
         <f t="shared" si="2"/>
         <v>1.6129032258064506</v>
       </c>
-      <c r="AB15" s="12">
+      <c r="AB15" s="11">
         <f t="shared" si="2"/>
         <v>1.6774193548387086</v>
       </c>
-      <c r="AC15" s="12">
+      <c r="AC15" s="11">
         <f t="shared" si="2"/>
         <v>1.7419354838709666</v>
       </c>
-      <c r="AD15" s="12">
+      <c r="AD15" s="11">
         <f t="shared" si="2"/>
         <v>1.8064516129032246</v>
       </c>
-      <c r="AE15" s="12">
+      <c r="AE15" s="11">
         <f t="shared" si="2"/>
         <v>1.8709677419354827</v>
       </c>
-      <c r="AF15" s="12">
+      <c r="AF15" s="11">
         <f t="shared" si="2"/>
         <v>1.9354838709677407</v>
       </c>
@@ -7724,123 +7724,123 @@
       <c r="B16" s="6">
         <v>0</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="11">
         <f t="shared" si="1"/>
         <v>6.4516129032258063E-2</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="11">
         <f t="shared" si="2"/>
         <v>0.12903225806451613</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="11">
         <f t="shared" si="2"/>
         <v>0.19354838709677419</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="11">
         <f t="shared" si="2"/>
         <v>0.25806451612903225</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="11">
         <f t="shared" si="2"/>
         <v>0.32258064516129031</v>
       </c>
-      <c r="H16" s="12">
+      <c r="H16" s="11">
         <f t="shared" si="2"/>
         <v>0.38709677419354838</v>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="11">
         <f t="shared" si="2"/>
         <v>0.45161290322580644</v>
       </c>
-      <c r="J16" s="12">
+      <c r="J16" s="11">
         <f t="shared" si="2"/>
         <v>0.5161290322580645</v>
       </c>
-      <c r="K16" s="12">
+      <c r="K16" s="11">
         <f t="shared" si="2"/>
         <v>0.58064516129032251</v>
       </c>
-      <c r="L16" s="12">
+      <c r="L16" s="11">
         <f t="shared" si="2"/>
         <v>0.64516129032258052</v>
       </c>
-      <c r="M16" s="12">
+      <c r="M16" s="11">
         <f t="shared" si="2"/>
         <v>0.70967741935483852</v>
       </c>
-      <c r="N16" s="12">
+      <c r="N16" s="11">
         <f t="shared" si="2"/>
         <v>0.77419354838709653</v>
       </c>
-      <c r="O16" s="12">
+      <c r="O16" s="11">
         <f t="shared" si="2"/>
         <v>0.83870967741935454</v>
       </c>
-      <c r="P16" s="12">
+      <c r="P16" s="11">
         <f t="shared" si="2"/>
         <v>0.90322580645161255</v>
       </c>
-      <c r="Q16" s="12">
+      <c r="Q16" s="11">
         <f t="shared" si="2"/>
         <v>0.96774193548387055</v>
       </c>
-      <c r="R16" s="12">
+      <c r="R16" s="11">
         <f t="shared" si="2"/>
         <v>1.0322580645161286</v>
       </c>
-      <c r="S16" s="12">
+      <c r="S16" s="11">
         <f t="shared" si="2"/>
         <v>1.0967741935483866</v>
       </c>
-      <c r="T16" s="12">
+      <c r="T16" s="11">
         <f t="shared" si="2"/>
         <v>1.1612903225806446</v>
       </c>
-      <c r="U16" s="12">
+      <c r="U16" s="11">
         <f t="shared" si="2"/>
         <v>1.2258064516129026</v>
       </c>
-      <c r="V16" s="12">
+      <c r="V16" s="11">
         <f t="shared" si="2"/>
         <v>1.2903225806451606</v>
       </c>
-      <c r="W16" s="12">
+      <c r="W16" s="11">
         <f t="shared" si="2"/>
         <v>1.3548387096774186</v>
       </c>
-      <c r="X16" s="12">
+      <c r="X16" s="11">
         <f t="shared" si="2"/>
         <v>1.4193548387096766</v>
       </c>
-      <c r="Y16" s="12">
+      <c r="Y16" s="11">
         <f t="shared" si="2"/>
         <v>1.4838709677419346</v>
       </c>
-      <c r="Z16" s="12">
+      <c r="Z16" s="11">
         <f t="shared" si="2"/>
         <v>1.5483870967741926</v>
       </c>
-      <c r="AA16" s="12">
+      <c r="AA16" s="11">
         <f t="shared" si="2"/>
         <v>1.6129032258064506</v>
       </c>
-      <c r="AB16" s="12">
+      <c r="AB16" s="11">
         <f t="shared" si="2"/>
         <v>1.6774193548387086</v>
       </c>
-      <c r="AC16" s="12">
+      <c r="AC16" s="11">
         <f t="shared" si="2"/>
         <v>1.7419354838709666</v>
       </c>
-      <c r="AD16" s="12">
+      <c r="AD16" s="11">
         <f t="shared" si="2"/>
         <v>1.8064516129032246</v>
       </c>
-      <c r="AE16" s="12">
+      <c r="AE16" s="11">
         <f t="shared" si="2"/>
         <v>1.8709677419354827</v>
       </c>
-      <c r="AF16" s="12">
+      <c r="AF16" s="11">
         <f t="shared" si="2"/>
         <v>1.9354838709677407</v>
       </c>
@@ -7850,128 +7850,128 @@
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" s="6">
         <v>0</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="11">
         <f t="shared" si="1"/>
         <v>6.4516129032258063E-2</v>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="11">
         <f t="shared" si="2"/>
         <v>0.12903225806451613</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="11">
         <f t="shared" si="2"/>
         <v>0.19354838709677419</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="11">
         <f t="shared" si="2"/>
         <v>0.25806451612903225</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="11">
         <f t="shared" si="2"/>
         <v>0.32258064516129031</v>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="11">
         <f t="shared" si="2"/>
         <v>0.38709677419354838</v>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="11">
         <f t="shared" si="2"/>
         <v>0.45161290322580644</v>
       </c>
-      <c r="J17" s="12">
+      <c r="J17" s="11">
         <f t="shared" si="2"/>
         <v>0.5161290322580645</v>
       </c>
-      <c r="K17" s="12">
+      <c r="K17" s="11">
         <f t="shared" si="2"/>
         <v>0.58064516129032251</v>
       </c>
-      <c r="L17" s="12">
+      <c r="L17" s="11">
         <f t="shared" si="2"/>
         <v>0.64516129032258052</v>
       </c>
-      <c r="M17" s="12">
+      <c r="M17" s="11">
         <f t="shared" si="2"/>
         <v>0.70967741935483852</v>
       </c>
-      <c r="N17" s="12">
+      <c r="N17" s="11">
         <f t="shared" si="2"/>
         <v>0.77419354838709653</v>
       </c>
-      <c r="O17" s="12">
+      <c r="O17" s="11">
         <f t="shared" si="2"/>
         <v>0.83870967741935454</v>
       </c>
-      <c r="P17" s="12">
+      <c r="P17" s="11">
         <f t="shared" si="2"/>
         <v>0.90322580645161255</v>
       </c>
-      <c r="Q17" s="12">
+      <c r="Q17" s="11">
         <f t="shared" si="2"/>
         <v>0.96774193548387055</v>
       </c>
-      <c r="R17" s="12">
+      <c r="R17" s="11">
         <f t="shared" si="2"/>
         <v>1.0322580645161286</v>
       </c>
-      <c r="S17" s="12">
+      <c r="S17" s="11">
         <f t="shared" si="2"/>
         <v>1.0967741935483866</v>
       </c>
-      <c r="T17" s="12">
+      <c r="T17" s="11">
         <f t="shared" si="2"/>
         <v>1.1612903225806446</v>
       </c>
-      <c r="U17" s="12">
+      <c r="U17" s="11">
         <f t="shared" si="2"/>
         <v>1.2258064516129026</v>
       </c>
-      <c r="V17" s="12">
+      <c r="V17" s="11">
         <f t="shared" si="2"/>
         <v>1.2903225806451606</v>
       </c>
-      <c r="W17" s="12">
+      <c r="W17" s="11">
         <f t="shared" si="2"/>
         <v>1.3548387096774186</v>
       </c>
-      <c r="X17" s="12">
+      <c r="X17" s="11">
         <f t="shared" si="2"/>
         <v>1.4193548387096766</v>
       </c>
-      <c r="Y17" s="12">
+      <c r="Y17" s="11">
         <f t="shared" si="2"/>
         <v>1.4838709677419346</v>
       </c>
-      <c r="Z17" s="12">
+      <c r="Z17" s="11">
         <f t="shared" si="2"/>
         <v>1.5483870967741926</v>
       </c>
-      <c r="AA17" s="12">
+      <c r="AA17" s="11">
         <f t="shared" si="2"/>
         <v>1.6129032258064506</v>
       </c>
-      <c r="AB17" s="12">
+      <c r="AB17" s="11">
         <f t="shared" si="2"/>
         <v>1.6774193548387086</v>
       </c>
-      <c r="AC17" s="12">
+      <c r="AC17" s="11">
         <f t="shared" si="2"/>
         <v>1.7419354838709666</v>
       </c>
-      <c r="AD17" s="12">
+      <c r="AD17" s="11">
         <f t="shared" si="2"/>
         <v>1.8064516129032246</v>
       </c>
-      <c r="AE17" s="12">
+      <c r="AE17" s="11">
         <f t="shared" si="2"/>
         <v>1.8709677419354827</v>
       </c>
-      <c r="AF17" s="12">
+      <c r="AF17" s="11">
         <f t="shared" si="2"/>
         <v>1.9354838709677407</v>
       </c>
@@ -7981,128 +7981,128 @@
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B18" s="6">
         <v>0</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="11">
         <f t="shared" si="1"/>
         <v>6.4516129032258063E-2</v>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="11">
         <f t="shared" si="2"/>
         <v>0.12903225806451613</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="11">
         <f t="shared" si="2"/>
         <v>0.19354838709677419</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="11">
         <f t="shared" si="2"/>
         <v>0.25806451612903225</v>
       </c>
-      <c r="G18" s="12">
+      <c r="G18" s="11">
         <f t="shared" si="2"/>
         <v>0.32258064516129031</v>
       </c>
-      <c r="H18" s="12">
+      <c r="H18" s="11">
         <f t="shared" si="2"/>
         <v>0.38709677419354838</v>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="11">
         <f t="shared" si="2"/>
         <v>0.45161290322580644</v>
       </c>
-      <c r="J18" s="12">
+      <c r="J18" s="11">
         <f t="shared" si="2"/>
         <v>0.5161290322580645</v>
       </c>
-      <c r="K18" s="12">
+      <c r="K18" s="11">
         <f t="shared" si="2"/>
         <v>0.58064516129032251</v>
       </c>
-      <c r="L18" s="12">
+      <c r="L18" s="11">
         <f t="shared" si="2"/>
         <v>0.64516129032258052</v>
       </c>
-      <c r="M18" s="12">
+      <c r="M18" s="11">
         <f t="shared" si="2"/>
         <v>0.70967741935483852</v>
       </c>
-      <c r="N18" s="12">
+      <c r="N18" s="11">
         <f t="shared" si="2"/>
         <v>0.77419354838709653</v>
       </c>
-      <c r="O18" s="12">
+      <c r="O18" s="11">
         <f t="shared" si="2"/>
         <v>0.83870967741935454</v>
       </c>
-      <c r="P18" s="12">
+      <c r="P18" s="11">
         <f t="shared" si="2"/>
         <v>0.90322580645161255</v>
       </c>
-      <c r="Q18" s="12">
+      <c r="Q18" s="11">
         <f t="shared" si="2"/>
         <v>0.96774193548387055</v>
       </c>
-      <c r="R18" s="12">
+      <c r="R18" s="11">
         <f t="shared" si="2"/>
         <v>1.0322580645161286</v>
       </c>
-      <c r="S18" s="12">
+      <c r="S18" s="11">
         <f t="shared" si="2"/>
         <v>1.0967741935483866</v>
       </c>
-      <c r="T18" s="12">
+      <c r="T18" s="11">
         <f t="shared" si="2"/>
         <v>1.1612903225806446</v>
       </c>
-      <c r="U18" s="12">
+      <c r="U18" s="11">
         <f t="shared" si="2"/>
         <v>1.2258064516129026</v>
       </c>
-      <c r="V18" s="12">
+      <c r="V18" s="11">
         <f t="shared" si="2"/>
         <v>1.2903225806451606</v>
       </c>
-      <c r="W18" s="12">
+      <c r="W18" s="11">
         <f t="shared" si="2"/>
         <v>1.3548387096774186</v>
       </c>
-      <c r="X18" s="12">
+      <c r="X18" s="11">
         <f t="shared" si="2"/>
         <v>1.4193548387096766</v>
       </c>
-      <c r="Y18" s="12">
+      <c r="Y18" s="11">
         <f t="shared" si="2"/>
         <v>1.4838709677419346</v>
       </c>
-      <c r="Z18" s="12">
+      <c r="Z18" s="11">
         <f t="shared" si="2"/>
         <v>1.5483870967741926</v>
       </c>
-      <c r="AA18" s="12">
+      <c r="AA18" s="11">
         <f t="shared" si="2"/>
         <v>1.6129032258064506</v>
       </c>
-      <c r="AB18" s="12">
+      <c r="AB18" s="11">
         <f t="shared" si="2"/>
         <v>1.6774193548387086</v>
       </c>
-      <c r="AC18" s="12">
+      <c r="AC18" s="11">
         <f t="shared" si="2"/>
         <v>1.7419354838709666</v>
       </c>
-      <c r="AD18" s="12">
+      <c r="AD18" s="11">
         <f t="shared" si="2"/>
         <v>1.8064516129032246</v>
       </c>
-      <c r="AE18" s="12">
+      <c r="AE18" s="11">
         <f t="shared" si="2"/>
         <v>1.8709677419354827</v>
       </c>
-      <c r="AF18" s="12">
+      <c r="AF18" s="11">
         <f t="shared" si="2"/>
         <v>1.9354838709677407</v>
       </c>
@@ -8111,25 +8111,25 @@
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A20" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="13"/>
-      <c r="M20" s="13"/>
+      <c r="A20" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="12"/>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -9568,7 +9568,7 @@
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B12" s="6">
         <v>1</v>
@@ -9964,7 +9964,7 @@
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15" s="6">
         <v>1</v>
@@ -10228,7 +10228,7 @@
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" s="6">
         <v>1</v>
@@ -10360,7 +10360,7 @@
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B18" s="6">
         <v>1</v>
@@ -10491,11 +10491,11 @@
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B20" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
+      <c r="B20" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
       <c r="E20" s="9">
         <v>0.01</v>
       </c>
@@ -11948,7 +11948,7 @@
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B12" s="5">
         <f t="shared" si="1"/>
@@ -12347,7 +12347,7 @@
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15" s="5">
         <f t="shared" si="1"/>
@@ -12613,7 +12613,7 @@
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" s="5">
         <f t="shared" si="1"/>
@@ -12746,7 +12746,7 @@
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B18" s="5">
         <f t="shared" si="1"/>
@@ -12878,18 +12878,18 @@
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B20" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
+      <c r="B20" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
       <c r="E20" s="10">
         <v>0.01</v>
       </c>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.3">
       <c r="E21" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
